--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -811,769 +811,775 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8393,0.0357,0.0758,0.0531</t>
-  </si>
-  <si>
-    <t>0.0387,0.0014,0.0001,0.9884</t>
-  </si>
-  <si>
-    <t>0.4077,0.0023,0.0107,0.7102</t>
-  </si>
-  <si>
-    <t>0.0146,0.0337,0.0065,0.9867</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9952,0.0005,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9806,0.0197,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9895,0.0059,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9936,0.0038,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9872,0.0101,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9935,0.0018,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9959,0.0006,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.6024,0.0335,0.4651,0.0080</t>
-  </si>
-  <si>
-    <t>0.2570,0.2237,0.5215,0.0055</t>
-  </si>
-  <si>
-    <t>0.6052,0.0210,0.5280,0.0008</t>
-  </si>
-  <si>
-    <t>0.1100,0.0054,0.9257,0.0021</t>
-  </si>
-  <si>
-    <t>0.7774,0.0265,0.2574,0.0071</t>
-  </si>
-  <si>
-    <t>0.0110,0.9844,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.0043,0.9871,0.0143,0.0014</t>
-  </si>
-  <si>
-    <t>0.5246,0.5768,0.0224,0.0051</t>
-  </si>
-  <si>
-    <t>0.0021,0.9933,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.9982,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.1880,0.0031,0.8365,0.0139</t>
-  </si>
-  <si>
-    <t>0.1404,0.1649,0.7160,0.1018</t>
-  </si>
-  <si>
-    <t>0.0381,0.0024,0.9729,0.0005</t>
-  </si>
-  <si>
-    <t>0.4976,0.0089,0.6789,0.0007</t>
-  </si>
-  <si>
-    <t>0.3085,0.0008,0.8681,0.0006</t>
-  </si>
-  <si>
-    <t>0.0104,0.0008,0.9821,0.0056</t>
-  </si>
-  <si>
-    <t>0.0111,0.0003,0.9868,0.0012</t>
-  </si>
-  <si>
-    <t>0.6341,0.5320,0.0059,0.0030</t>
-  </si>
-  <si>
-    <t>0.6256,0.2019,0.2200,0.0063</t>
-  </si>
-  <si>
-    <t>0.0010,0.0069,0.9946,0.0038</t>
-  </si>
-  <si>
-    <t>0.0067,0.9760,0.0362,0.0002</t>
-  </si>
-  <si>
-    <t>0.9021,0.0483,0.0208,0.0395</t>
-  </si>
-  <si>
-    <t>0.8241,0.0247,0.1772,0.0065</t>
-  </si>
-  <si>
-    <t>0.6279,0.4142,0.0246,0.0040</t>
-  </si>
-  <si>
-    <t>0.0379,0.9045,0.3800,0.0049</t>
-  </si>
-  <si>
-    <t>0.0255,0.5774,0.8359,0.0202</t>
-  </si>
-  <si>
-    <t>0.1315,0.0012,0.8197,0.0239</t>
-  </si>
-  <si>
-    <t>0.0467,0.0180,0.9488,0.0047</t>
-  </si>
-  <si>
-    <t>0.0413,0.0129,0.9083,0.0491</t>
-  </si>
-  <si>
-    <t>0.0237,0.1955,0.9467,0.0011</t>
-  </si>
-  <si>
-    <t>0.0550,0.9371,0.0093,0.0014</t>
-  </si>
-  <si>
-    <t>0.0074,0.0202,0.9696,0.0140</t>
-  </si>
-  <si>
-    <t>0.0079,0.8688,0.0034,0.7806</t>
-  </si>
-  <si>
-    <t>0.0152,0.9738,0.0043,0.0023</t>
-  </si>
-  <si>
-    <t>0.0089,0.9438,0.2840,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.9942,0.0666,0.0003</t>
-  </si>
-  <si>
-    <t>0.0095,0.0580,0.9457,0.0169</t>
-  </si>
-  <si>
-    <t>0.0102,0.0193,0.9831,0.0005</t>
-  </si>
-  <si>
-    <t>0.0089,0.0015,0.9806,0.0127</t>
-  </si>
-  <si>
-    <t>0.0092,0.0010,0.9906,0.0004</t>
-  </si>
-  <si>
-    <t>0.0167,0.0030,0.9750,0.0043</t>
-  </si>
-  <si>
-    <t>0.0510,0.0102,0.9465,0.0015</t>
-  </si>
-  <si>
-    <t>0.9145,0.1095,0.0024,0.0022</t>
-  </si>
-  <si>
-    <t>0.9781,0.0073,0.0069,0.0034</t>
-  </si>
-  <si>
-    <t>0.9828,0.0195,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.0024,0.0153,0.9929,0.0024</t>
-  </si>
-  <si>
-    <t>0.9298,0.0565,0.0242,0.0033</t>
-  </si>
-  <si>
-    <t>0.9937,0.0010,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9442,0.0719,0.0049,0.0019</t>
-  </si>
-  <si>
-    <t>0.0066,0.9122,0.7103,0.0023</t>
-  </si>
-  <si>
-    <t>0.0064,0.0084,0.9855,0.0024</t>
-  </si>
-  <si>
-    <t>0.0033,0.0145,0.9747,0.0279</t>
-  </si>
-  <si>
-    <t>0.0002,0.8995,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.0109,0.0045,0.9797,0.0039</t>
-  </si>
-  <si>
-    <t>0.1016,0.7569,0.1140,0.0005</t>
-  </si>
-  <si>
-    <t>0.0120,0.9839,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.5000,0.0918,0.5040,0.0055</t>
-  </si>
-  <si>
-    <t>0.8130,0.1580,0.0479,0.0063</t>
-  </si>
-  <si>
-    <t>0.0034,0.0592,0.9844,0.0028</t>
-  </si>
-  <si>
-    <t>0.0349,0.4408,0.8595,0.0025</t>
-  </si>
-  <si>
-    <t>0.0014,0.5541,0.9717,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9874,0.2972,0.0007</t>
-  </si>
-  <si>
-    <t>0.0017,0.8472,0.8937,0.0003</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.0464,0.9863</t>
-  </si>
-  <si>
-    <t>0.0011,0.0046,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.0112,0.0009,0.0000,0.9966</t>
-  </si>
-  <si>
-    <t>0.0038,0.0020,0.0054,0.9947</t>
-  </si>
-  <si>
-    <t>0.0092,0.0249,0.0445,0.9768</t>
-  </si>
-  <si>
-    <t>0.0052,0.0013,0.0105,0.9926</t>
-  </si>
-  <si>
-    <t>0.0006,0.9804,0.8648,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.7293,0.9543,0.0001</t>
-  </si>
-  <si>
-    <t>0.0167,0.1161,0.9503,0.0006</t>
-  </si>
-  <si>
-    <t>0.0042,0.4991,0.9559,0.0009</t>
-  </si>
-  <si>
-    <t>0.0031,0.7418,0.8346,0.0001</t>
-  </si>
-  <si>
-    <t>0.0080,0.6215,0.8347,0.0003</t>
-  </si>
-  <si>
-    <t>0.9845,0.0175,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9793,0.0327,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9609,0.0262,0.0020,0.0033</t>
-  </si>
-  <si>
-    <t>0.9923,0.0020,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.9687,0.0164,0.0049,0.0035</t>
-  </si>
-  <si>
-    <t>0.9963,0.0017,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9729,0.0187,0.0070,0.0015</t>
-  </si>
-  <si>
-    <t>0.9457,0.0492,0.0099,0.0036</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9939,0.0019,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0004,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9962,0.0006,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9953,0.0007,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9963,0.0006,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.9976,0.0009</t>
-  </si>
-  <si>
-    <t>0.2930,0.0070,0.8168,0.0025</t>
-  </si>
-  <si>
-    <t>0.7035,0.0176,0.3157,0.0244</t>
-  </si>
-  <si>
-    <t>0.0557,0.0086,0.9437,0.0037</t>
-  </si>
-  <si>
-    <t>0.0035,0.9898,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.0635,0.9221,0.0021,0.0040</t>
-  </si>
-  <si>
-    <t>0.0265,0.9584,0.0027,0.0040</t>
-  </si>
-  <si>
-    <t>0.6686,0.4042,0.0121,0.0030</t>
-  </si>
-  <si>
-    <t>0.0127,0.9738,0.0019,0.0046</t>
-  </si>
-  <si>
-    <t>0.0051,0.9883,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.6676,0.3342,0.0465,0.0024</t>
-  </si>
-  <si>
-    <t>0.6884,0.0523,0.2717,0.0350</t>
-  </si>
-  <si>
-    <t>0.7197,0.0125,0.4301,0.0025</t>
-  </si>
-  <si>
-    <t>0.7077,0.1456,0.1140,0.0402</t>
-  </si>
-  <si>
-    <t>0.4655,0.0219,0.6176,0.0127</t>
-  </si>
-  <si>
-    <t>0.0281,0.2159,0.0092,0.9663</t>
-  </si>
-  <si>
-    <t>0.0036,0.9919,0.0086,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.9933,0.0006,0.0088</t>
-  </si>
-  <si>
-    <t>0.0377,0.9077,0.0254,0.0660</t>
-  </si>
-  <si>
-    <t>0.0016,0.9569,0.6138,0.0023</t>
-  </si>
-  <si>
-    <t>0.0440,0.9739,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.7349,0.4015,0.0099,0.0009</t>
-  </si>
-  <si>
-    <t>0.1980,0.8412,0.0108,0.0027</t>
-  </si>
-  <si>
-    <t>0.9817,0.0096,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.9834,0.0031,0.0012,0.0058</t>
-  </si>
-  <si>
-    <t>0.9865,0.0030,0.0018,0.0036</t>
-  </si>
-  <si>
-    <t>0.9478,0.0189,0.0130,0.0138</t>
-  </si>
-  <si>
-    <t>0.9886,0.0026,0.0008,0.0031</t>
-  </si>
-  <si>
-    <t>0.9399,0.0117,0.0307,0.0108</t>
-  </si>
-  <si>
-    <t>0.9825,0.0043,0.0044,0.0040</t>
-  </si>
-  <si>
-    <t>0.9714,0.0032,0.0132,0.0047</t>
-  </si>
-  <si>
-    <t>0.0033,0.4607,0.9622,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.9502,0.8879,0.0000</t>
-  </si>
-  <si>
-    <t>0.0501,0.0340,0.9329,0.0018</t>
-  </si>
-  <si>
-    <t>0.0511,0.1480,0.8787,0.0007</t>
-  </si>
-  <si>
-    <t>0.6329,0.1321,0.1711,0.2363</t>
-  </si>
-  <si>
-    <t>0.5185,0.4927,0.0355,0.0102</t>
-  </si>
-  <si>
-    <t>0.7126,0.0095,0.4584,0.0026</t>
-  </si>
-  <si>
-    <t>0.7925,0.1085,0.0748,0.0110</t>
-  </si>
-  <si>
-    <t>0.0665,0.0018,0.0046,0.9654</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0116,0.0053,0.0005,0.9948</t>
-  </si>
-  <si>
-    <t>0.0242,0.0009,0.0010,0.9910</t>
-  </si>
-  <si>
-    <t>0.0059,0.8169,0.5242,0.0251</t>
-  </si>
-  <si>
-    <t>0.9850,0.0051,0.0014,0.0029</t>
-  </si>
-  <si>
-    <t>0.1274,0.8538,0.0053,0.0279</t>
-  </si>
-  <si>
-    <t>0.9805,0.0018,0.0009,0.0088</t>
-  </si>
-  <si>
-    <t>0.8884,0.1106,0.0166,0.0030</t>
-  </si>
-  <si>
-    <t>0.9768,0.0072,0.0055,0.0035</t>
-  </si>
-  <si>
-    <t>0.5538,0.0066,0.0270,0.5055</t>
-  </si>
-  <si>
-    <t>0.9665,0.0068,0.0033,0.0162</t>
-  </si>
-  <si>
-    <t>0.0012,0.0246,0.9802,0.0323</t>
-  </si>
-  <si>
-    <t>0.9044,0.0020,0.0054,0.0900</t>
-  </si>
-  <si>
-    <t>0.9420,0.0014,0.0029,0.0526</t>
-  </si>
-  <si>
-    <t>0.1995,0.6811,0.0258,0.1322</t>
-  </si>
-  <si>
-    <t>0.9559,0.0164,0.0162,0.0007</t>
-  </si>
-  <si>
-    <t>0.8502,0.1669,0.0170,0.0009</t>
-  </si>
-  <si>
-    <t>0.6820,0.2893,0.0838,0.0290</t>
-  </si>
-  <si>
-    <t>0.8621,0.0400,0.1013,0.0093</t>
-  </si>
-  <si>
-    <t>0.9452,0.0439,0.0094,0.0009</t>
-  </si>
-  <si>
-    <t>0.9841,0.0046,0.0017,0.0026</t>
-  </si>
-  <si>
-    <t>0.9912,0.0027,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9846,0.0011,0.0007,0.0092</t>
-  </si>
-  <si>
-    <t>0.9832,0.0005,0.0007,0.0152</t>
-  </si>
-  <si>
-    <t>0.9720,0.0154,0.0034,0.0035</t>
-  </si>
-  <si>
-    <t>0.9575,0.0331,0.0069,0.0034</t>
-  </si>
-  <si>
-    <t>0.9827,0.0074,0.0019,0.0026</t>
-  </si>
-  <si>
-    <t>0.9879,0.0009,0.0003,0.0071</t>
-  </si>
-  <si>
-    <t>0.9073,0.1095,0.0068,0.0059</t>
-  </si>
-  <si>
-    <t>0.6638,0.4505,0.0105,0.0005</t>
-  </si>
-  <si>
-    <t>0.5068,0.5662,0.0205,0.0025</t>
-  </si>
-  <si>
-    <t>0.1904,0.3810,0.7028,0.0055</t>
-  </si>
-  <si>
-    <t>0.9664,0.0216,0.0051,0.0030</t>
-  </si>
-  <si>
-    <t>0.8596,0.1610,0.0125,0.0056</t>
-  </si>
-  <si>
-    <t>0.9630,0.0337,0.0049,0.0019</t>
-  </si>
-  <si>
-    <t>0.8588,0.1381,0.0295,0.0078</t>
-  </si>
-  <si>
-    <t>0.0008,0.0458,0.9961,0.0006</t>
-  </si>
-  <si>
-    <t>0.9214,0.0690,0.0195,0.0022</t>
-  </si>
-  <si>
-    <t>0.0117,0.0023,0.9845,0.0010</t>
-  </si>
-  <si>
-    <t>0.0053,0.0653,0.9814,0.0016</t>
-  </si>
-  <si>
-    <t>0.1014,0.0029,0.9310,0.0029</t>
-  </si>
-  <si>
-    <t>0.0905,0.1430,0.8162,0.0166</t>
-  </si>
-  <si>
-    <t>0.0141,0.0193,0.9710,0.0012</t>
-  </si>
-  <si>
-    <t>0.0011,0.0069,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0333,0.0037,0.9646,0.0019</t>
-  </si>
-  <si>
-    <t>0.3419,0.0083,0.7754,0.0041</t>
-  </si>
-  <si>
-    <t>0.3199,0.0180,0.7581,0.0037</t>
-  </si>
-  <si>
-    <t>0.5444,0.0522,0.5268,0.0111</t>
-  </si>
-  <si>
-    <t>0.3886,0.2794,0.2799,0.0158</t>
-  </si>
-  <si>
-    <t>0.2696,0.0717,0.6737,0.0119</t>
-  </si>
-  <si>
-    <t>0.4046,0.0972,0.4503,0.0020</t>
-  </si>
-  <si>
-    <t>0.7908,0.0436,0.1559,0.0221</t>
-  </si>
-  <si>
-    <t>0.7170,0.0507,0.2660,0.0133</t>
-  </si>
-  <si>
-    <t>0.5304,0.6534,0.0037,0.0006</t>
-  </si>
-  <si>
-    <t>0.1780,0.8916,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.8828,0.2013,0.0057,0.0005</t>
-  </si>
-  <si>
-    <t>0.9593,0.0349,0.0014,0.0025</t>
-  </si>
-  <si>
-    <t>0.8347,0.2283,0.0107,0.0006</t>
-  </si>
-  <si>
-    <t>0.4879,0.2983,0.2311,0.0254</t>
-  </si>
-  <si>
-    <t>0.8029,0.0095,0.1292,0.0303</t>
-  </si>
-  <si>
-    <t>0.8880,0.0047,0.0823,0.0078</t>
-  </si>
-  <si>
-    <t>0.6224,0.0149,0.4228,0.0107</t>
-  </si>
-  <si>
-    <t>0.9199,0.0065,0.0429,0.0153</t>
-  </si>
-  <si>
-    <t>0.1101,0.0426,0.8308,0.0434</t>
-  </si>
-  <si>
-    <t>0.0325,0.2217,0.9240,0.0028</t>
-  </si>
-  <si>
-    <t>0.0204,0.1972,0.9337,0.0055</t>
-  </si>
-  <si>
-    <t>0.1299,0.0215,0.8978,0.0048</t>
-  </si>
-  <si>
-    <t>0.0403,0.0363,0.9295,0.0028</t>
-  </si>
-  <si>
-    <t>0.9964,0.0006,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9853,0.0113,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9813,0.0111,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9873,0.0047,0.0013,0.0019</t>
-  </si>
-  <si>
-    <t>0.9937,0.0015,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9637,0.0243,0.0119,0.0020</t>
-  </si>
-  <si>
-    <t>0.9905,0.0006,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.9873,0.0079,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.1572,0.0088,0.8959,0.0034</t>
-  </si>
-  <si>
-    <t>0.0778,0.5342,0.5515,0.0012</t>
-  </si>
-  <si>
-    <t>0.8091,0.0144,0.1730,0.0111</t>
-  </si>
-  <si>
-    <t>0.0239,0.0048,0.9822,0.0002</t>
-  </si>
-  <si>
-    <t>0.0089,0.0136,0.9850,0.0008</t>
-  </si>
-  <si>
-    <t>0.0136,0.1299,0.9537,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.0312,0.0196,0.9487,0.0006</t>
-  </si>
-  <si>
-    <t>0.0051,0.0061,0.9903,0.0010</t>
-  </si>
-  <si>
-    <t>0.0428,0.0045,0.9551,0.0027</t>
-  </si>
-  <si>
-    <t>0.0416,0.0379,0.9351,0.0046</t>
-  </si>
-  <si>
-    <t>0.7241,0.0062,0.3177,0.0135</t>
-  </si>
-  <si>
-    <t>0.5572,0.0056,0.5828,0.0063</t>
-  </si>
-  <si>
-    <t>0.9004,0.0180,0.0709,0.0055</t>
-  </si>
-  <si>
-    <t>0.9933,0.0029,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9779,0.0263,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9379,0.0814,0.0086,0.0011</t>
-  </si>
-  <si>
-    <t>0.9955,0.0004,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9798,0.0177,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9868,0.0088,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9949,0.0004,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.0353,0.7222,0.2540,0.0067</t>
-  </si>
-  <si>
-    <t>0.0166,0.0028,0.9804,0.0015</t>
-  </si>
-  <si>
-    <t>0.0155,0.0515,0.9650,0.0061</t>
-  </si>
-  <si>
-    <t>0.0394,0.0115,0.9550,0.0013</t>
-  </si>
-  <si>
-    <t>0.0209,0.0022,0.9722,0.0051</t>
-  </si>
-  <si>
-    <t>0.0821,0.0051,0.5967,0.4182</t>
-  </si>
-  <si>
-    <t>0.1445,0.0206,0.8467,0.0413</t>
-  </si>
-  <si>
-    <t>0.0092,0.0384,0.8362,0.1416</t>
-  </si>
-  <si>
-    <t>0.5594,0.0010,0.0081,0.5404</t>
-  </si>
-  <si>
-    <t>0.0179,0.1568,0.0045,0.9755</t>
-  </si>
-  <si>
-    <t>0.0557,0.0041,0.0006,0.9835</t>
-  </si>
-  <si>
-    <t>0.0016,0.0000,0.0008,0.9984</t>
-  </si>
-  <si>
-    <t>0.0046,0.0002,0.0001,0.9981</t>
-  </si>
-  <si>
-    <t>0.4136,0.0279,0.0035,0.6684</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.6382,0.1226,0.0298,0.1891</t>
+  </si>
+  <si>
+    <t>0.0263,0.0048,0.0052,0.9839</t>
+  </si>
+  <si>
+    <t>0.6806,0.0224,0.0177,0.3564</t>
+  </si>
+  <si>
+    <t>0.0087,0.0034,0.0029,0.9942</t>
+  </si>
+  <si>
+    <t>0.9969,0.0012,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0020,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9734,0.0074,0.0139,0.0024</t>
+  </si>
+  <si>
+    <t>0.9935,0.0030,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9915,0.0041,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9884,0.0067,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9950,0.0014,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0008,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.8742,0.0329,0.1025,0.0016</t>
+  </si>
+  <si>
+    <t>0.1547,0.0712,0.8160,0.0076</t>
+  </si>
+  <si>
+    <t>0.4987,0.0058,0.7293,0.0006</t>
+  </si>
+  <si>
+    <t>0.0697,0.0090,0.9508,0.0003</t>
+  </si>
+  <si>
+    <t>0.7464,0.0404,0.3035,0.0070</t>
+  </si>
+  <si>
+    <t>0.1887,0.8754,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.9921,0.0184,0.0002</t>
+  </si>
+  <si>
+    <t>0.1755,0.8585,0.0097,0.0041</t>
+  </si>
+  <si>
+    <t>0.0232,0.9691,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.0013,0.9941,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.8358,0.0013,0.3382,0.0008</t>
+  </si>
+  <si>
+    <t>0.6637,0.0113,0.2616,0.0325</t>
+  </si>
+  <si>
+    <t>0.0130,0.0047,0.9815,0.0014</t>
+  </si>
+  <si>
+    <t>0.3415,0.0031,0.8075,0.0018</t>
+  </si>
+  <si>
+    <t>0.1098,0.0022,0.9353,0.0016</t>
+  </si>
+  <si>
+    <t>0.2607,0.0045,0.8501,0.0013</t>
+  </si>
+  <si>
+    <t>0.0084,0.0015,0.9889,0.0013</t>
+  </si>
+  <si>
+    <t>0.7731,0.3953,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.1825,0.1574,0.7716,0.0229</t>
+  </si>
+  <si>
+    <t>0.0011,0.0028,0.9959,0.0045</t>
+  </si>
+  <si>
+    <t>0.0764,0.7143,0.2302,0.0008</t>
+  </si>
+  <si>
+    <t>0.8757,0.0887,0.0292,0.0122</t>
+  </si>
+  <si>
+    <t>0.8741,0.1177,0.0235,0.0073</t>
+  </si>
+  <si>
+    <t>0.6676,0.4794,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.0178,0.9632,0.0954,0.0014</t>
+  </si>
+  <si>
+    <t>0.0245,0.1945,0.7431,0.1116</t>
+  </si>
+  <si>
+    <t>0.0249,0.0102,0.8879,0.0798</t>
+  </si>
+  <si>
+    <t>0.1583,0.0277,0.8237,0.0227</t>
+  </si>
+  <si>
+    <t>0.0807,0.0017,0.9298,0.0058</t>
+  </si>
+  <si>
+    <t>0.0401,0.0415,0.9311,0.0078</t>
+  </si>
+  <si>
+    <t>0.0180,0.8681,0.1725,0.0042</t>
+  </si>
+  <si>
+    <t>0.0337,0.0598,0.9030,0.0256</t>
+  </si>
+  <si>
+    <t>0.0084,0.8403,0.0243,0.8384</t>
+  </si>
+  <si>
+    <t>0.0052,0.9894,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.0148,0.9672,0.0760,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.9945,0.0051,0.0012</t>
+  </si>
+  <si>
+    <t>0.0231,0.0545,0.9415,0.0175</t>
+  </si>
+  <si>
+    <t>0.0006,0.0187,0.9961,0.0008</t>
+  </si>
+  <si>
+    <t>0.2089,0.0038,0.8468,0.0056</t>
+  </si>
+  <si>
+    <t>0.0207,0.0007,0.9798,0.0012</t>
+  </si>
+  <si>
+    <t>0.0004,0.0159,0.9948,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.0085,0.9927,0.0017</t>
+  </si>
+  <si>
+    <t>0.8908,0.1429,0.0117,0.0031</t>
+  </si>
+  <si>
+    <t>0.9664,0.0084,0.0034,0.0120</t>
+  </si>
+  <si>
+    <t>0.9704,0.0112,0.0085,0.0042</t>
+  </si>
+  <si>
+    <t>0.0039,0.0492,0.9849,0.0059</t>
+  </si>
+  <si>
+    <t>0.9548,0.0256,0.0155,0.0040</t>
+  </si>
+  <si>
+    <t>0.9929,0.0040,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9843,0.0114,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.0037,0.6407,0.9287,0.0070</t>
+  </si>
+  <si>
+    <t>0.0071,0.0894,0.9817,0.0020</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9828,0.0746</t>
+  </si>
+  <si>
+    <t>0.0004,0.9505,0.9654,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0024,0.9946,0.0008</t>
+  </si>
+  <si>
+    <t>0.0226,0.9137,0.1083,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.9813,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.4043,0.0787,0.6300,0.0043</t>
+  </si>
+  <si>
+    <t>0.6519,0.3614,0.0676,0.0041</t>
+  </si>
+  <si>
+    <t>0.0035,0.0625,0.9785,0.0038</t>
+  </si>
+  <si>
+    <t>0.0009,0.8964,0.9145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9526,0.8224,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9943,0.0739,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.9090,0.8747,0.0004</t>
+  </si>
+  <si>
+    <t>0.0248,0.0003,0.0129,0.9731</t>
+  </si>
+  <si>
+    <t>0.0070,0.0005,0.0002,0.9974</t>
+  </si>
+  <si>
+    <t>0.0313,0.0004,0.0000,0.9927</t>
+  </si>
+  <si>
+    <t>0.0033,0.0044,0.0014,0.9966</t>
+  </si>
+  <si>
+    <t>0.0121,0.0038,0.0466,0.9758</t>
+  </si>
+  <si>
+    <t>0.0313,0.0027,0.0002,0.9912</t>
+  </si>
+  <si>
+    <t>0.0005,0.9841,0.8677,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.7984,0.9404,0.0005</t>
+  </si>
+  <si>
+    <t>0.0599,0.4741,0.7287,0.0088</t>
+  </si>
+  <si>
+    <t>0.0022,0.6021,0.9709,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9625,0.6632,0.0000</t>
+  </si>
+  <si>
+    <t>0.0116,0.5994,0.8051,0.0067</t>
+  </si>
+  <si>
+    <t>0.9768,0.0295,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9851,0.0170,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9654,0.0511,0.0032,0.0007</t>
+  </si>
+  <si>
+    <t>0.9836,0.0090,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9799,0.0080,0.0008,0.0029</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9663,0.0347,0.0031,0.0020</t>
+  </si>
+  <si>
+    <t>0.9565,0.0330,0.0119,0.0030</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9909,0.0017,0.0008,0.0033</t>
+  </si>
+  <si>
+    <t>0.9950,0.0019,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0107,0.0007,0.9842,0.0033</t>
+  </si>
+  <si>
+    <t>0.0376,0.0067,0.9723,0.0005</t>
+  </si>
+  <si>
+    <t>0.8584,0.0078,0.1458,0.0074</t>
+  </si>
+  <si>
+    <t>0.1329,0.0022,0.9345,0.0004</t>
+  </si>
+  <si>
+    <t>0.0356,0.9459,0.0126,0.0043</t>
+  </si>
+  <si>
+    <t>0.0074,0.9837,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.1234,0.8813,0.0055,0.0030</t>
+  </si>
+  <si>
+    <t>0.3300,0.7440,0.0054,0.0038</t>
+  </si>
+  <si>
+    <t>0.0074,0.9834,0.0024,0.0017</t>
+  </si>
+  <si>
+    <t>0.0038,0.9896,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.7570,0.3263,0.0138,0.0015</t>
+  </si>
+  <si>
+    <t>0.5994,0.2265,0.0281,0.0824</t>
+  </si>
+  <si>
+    <t>0.5987,0.0047,0.5320,0.0083</t>
+  </si>
+  <si>
+    <t>0.7146,0.1380,0.0572,0.0455</t>
+  </si>
+  <si>
+    <t>0.7417,0.0176,0.3619,0.0044</t>
+  </si>
+  <si>
+    <t>0.1495,0.0330,0.0288,0.9101</t>
+  </si>
+  <si>
+    <t>0.0206,0.9784,0.0104,0.0001</t>
+  </si>
+  <si>
+    <t>0.0386,0.9550,0.0060,0.0028</t>
+  </si>
+  <si>
+    <t>0.0189,0.9496,0.0139,0.0670</t>
+  </si>
+  <si>
+    <t>0.0016,0.8822,0.9356,0.0005</t>
+  </si>
+  <si>
+    <t>0.0179,0.9825,0.0144,0.0001</t>
+  </si>
+  <si>
+    <t>0.7293,0.3023,0.0395,0.0073</t>
+  </si>
+  <si>
+    <t>0.3249,0.7425,0.0147,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0068,0.0009,0.0026</t>
+  </si>
+  <si>
+    <t>0.9865,0.0045,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.9753,0.0075,0.0121,0.0023</t>
+  </si>
+  <si>
+    <t>0.9612,0.0113,0.0054,0.0106</t>
+  </si>
+  <si>
+    <t>0.9862,0.0014,0.0009,0.0066</t>
+  </si>
+  <si>
+    <t>0.9804,0.0046,0.0113,0.0012</t>
+  </si>
+  <si>
+    <t>0.9613,0.0027,0.0173,0.0066</t>
+  </si>
+  <si>
+    <t>0.9816,0.0031,0.0040,0.0044</t>
+  </si>
+  <si>
+    <t>0.0056,0.4403,0.9583,0.0005</t>
+  </si>
+  <si>
+    <t>0.0063,0.0979,0.9802,0.0001</t>
+  </si>
+  <si>
+    <t>0.0453,0.1264,0.8909,0.0021</t>
+  </si>
+  <si>
+    <t>0.0049,0.0273,0.9833,0.0014</t>
+  </si>
+  <si>
+    <t>0.8324,0.0191,0.1621,0.0048</t>
+  </si>
+  <si>
+    <t>0.7558,0.1037,0.1255,0.0262</t>
+  </si>
+  <si>
+    <t>0.4433,0.0028,0.7358,0.0023</t>
+  </si>
+  <si>
+    <t>0.6020,0.2903,0.1034,0.0302</t>
+  </si>
+  <si>
+    <t>0.0323,0.0004,0.0009,0.9883</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0025,0.0150,0.0005,0.9977</t>
+  </si>
+  <si>
+    <t>0.0046,0.0010,0.0065,0.9944</t>
+  </si>
+  <si>
+    <t>0.0012,0.7351,0.8973,0.0038</t>
+  </si>
+  <si>
+    <t>0.9571,0.0214,0.0098,0.0060</t>
+  </si>
+  <si>
+    <t>0.4997,0.4935,0.0103,0.0326</t>
+  </si>
+  <si>
+    <t>0.9777,0.0066,0.0011,0.0042</t>
+  </si>
+  <si>
+    <t>0.8209,0.2214,0.0178,0.0011</t>
+  </si>
+  <si>
+    <t>0.8465,0.0034,0.0521,0.0447</t>
+  </si>
+  <si>
+    <t>0.0902,0.0033,0.0002,0.9693</t>
+  </si>
+  <si>
+    <t>0.9784,0.0101,0.0019,0.0032</t>
+  </si>
+  <si>
+    <t>0.0002,0.0265,0.9951,0.0053</t>
+  </si>
+  <si>
+    <t>0.9218,0.0002,0.0005,0.1216</t>
+  </si>
+  <si>
+    <t>0.9516,0.0069,0.0052,0.0295</t>
+  </si>
+  <si>
+    <t>0.6912,0.3688,0.0140,0.0123</t>
+  </si>
+  <si>
+    <t>0.9448,0.0155,0.0215,0.0024</t>
+  </si>
+  <si>
+    <t>0.9667,0.0267,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.3060,0.6539,0.0664,0.0095</t>
+  </si>
+  <si>
+    <t>0.8244,0.1568,0.0302,0.0005</t>
+  </si>
+  <si>
+    <t>0.9455,0.0482,0.0063,0.0008</t>
+  </si>
+  <si>
+    <t>0.9870,0.0023,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.9888,0.0018,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.9932,0.0014,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9948,0.0007,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9752,0.0094,0.0038,0.0043</t>
+  </si>
+  <si>
+    <t>0.9637,0.0116,0.0046,0.0102</t>
+  </si>
+  <si>
+    <t>0.9868,0.0013,0.0007,0.0054</t>
+  </si>
+  <si>
+    <t>0.9880,0.0019,0.0008,0.0028</t>
+  </si>
+  <si>
+    <t>0.9180,0.0921,0.0017,0.0023</t>
+  </si>
+  <si>
+    <t>0.8528,0.1847,0.0102,0.0004</t>
+  </si>
+  <si>
+    <t>0.2553,0.7622,0.0097,0.0107</t>
+  </si>
+  <si>
+    <t>0.5547,0.3920,0.1254,0.0477</t>
+  </si>
+  <si>
+    <t>0.9367,0.0724,0.0040,0.0035</t>
+  </si>
+  <si>
+    <t>0.8913,0.0435,0.0394,0.0363</t>
+  </si>
+  <si>
+    <t>0.7877,0.2063,0.0454,0.0138</t>
+  </si>
+  <si>
+    <t>0.7461,0.3100,0.0094,0.0028</t>
+  </si>
+  <si>
+    <t>0.0003,0.1586,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.8430,0.1273,0.0293,0.0156</t>
+  </si>
+  <si>
+    <t>0.0046,0.0036,0.9921,0.0002</t>
+  </si>
+  <si>
+    <t>0.0308,0.0151,0.9548,0.0047</t>
+  </si>
+  <si>
+    <t>0.0209,0.0023,0.9806,0.0010</t>
+  </si>
+  <si>
+    <t>0.0361,0.0352,0.9588,0.0010</t>
+  </si>
+  <si>
+    <t>0.0234,0.0547,0.9275,0.0013</t>
+  </si>
+  <si>
+    <t>0.0092,0.0024,0.9908,0.0002</t>
+  </si>
+  <si>
+    <t>0.0410,0.0073,0.9713,0.0004</t>
+  </si>
+  <si>
+    <t>0.3607,0.0365,0.6942,0.0075</t>
+  </si>
+  <si>
+    <t>0.0413,0.0332,0.9058,0.0065</t>
+  </si>
+  <si>
+    <t>0.5694,0.0180,0.6381,0.0014</t>
+  </si>
+  <si>
+    <t>0.6908,0.0529,0.3284,0.0016</t>
+  </si>
+  <si>
+    <t>0.0863,0.6109,0.4646,0.0121</t>
+  </si>
+  <si>
+    <t>0.7165,0.0642,0.2819,0.0062</t>
+  </si>
+  <si>
+    <t>0.7560,0.0233,0.2367,0.0289</t>
+  </si>
+  <si>
+    <t>0.4215,0.0097,0.7483,0.0015</t>
+  </si>
+  <si>
+    <t>0.8291,0.3292,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.4524,0.5551,0.0205,0.0004</t>
+  </si>
+  <si>
+    <t>0.8639,0.1879,0.0154,0.0018</t>
+  </si>
+  <si>
+    <t>0.8932,0.1252,0.0058,0.0032</t>
+  </si>
+  <si>
+    <t>0.4129,0.6937,0.0051,0.0015</t>
+  </si>
+  <si>
+    <t>0.3837,0.3183,0.3208,0.0166</t>
+  </si>
+  <si>
+    <t>0.8280,0.0278,0.1438,0.0076</t>
+  </si>
+  <si>
+    <t>0.8876,0.0051,0.1008,0.0074</t>
+  </si>
+  <si>
+    <t>0.3049,0.0499,0.6890,0.0120</t>
+  </si>
+  <si>
+    <t>0.6330,0.0080,0.3565,0.0294</t>
+  </si>
+  <si>
+    <t>0.0064,0.0137,0.9665,0.0407</t>
+  </si>
+  <si>
+    <t>0.0223,0.6207,0.8691,0.0048</t>
+  </si>
+  <si>
+    <t>0.0379,0.0176,0.9517,0.0040</t>
+  </si>
+  <si>
+    <t>0.1754,0.0126,0.8522,0.0083</t>
+  </si>
+  <si>
+    <t>0.0193,0.1790,0.8108,0.0226</t>
+  </si>
+  <si>
+    <t>0.9904,0.0023,0.0012,0.0020</t>
+  </si>
+  <si>
+    <t>0.9926,0.0027,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9866,0.0045,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9927,0.0027,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9715,0.0168,0.0064,0.0023</t>
+  </si>
+  <si>
+    <t>0.9834,0.0067,0.0021,0.0029</t>
+  </si>
+  <si>
+    <t>0.9954,0.0004,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.9820,0.0098,0.0043,0.0009</t>
+  </si>
+  <si>
+    <t>0.3578,0.0091,0.7882,0.0044</t>
+  </si>
+  <si>
+    <t>0.1619,0.5811,0.4520,0.0067</t>
+  </si>
+  <si>
+    <t>0.8525,0.0459,0.0739,0.0262</t>
+  </si>
+  <si>
+    <t>0.0313,0.0200,0.9575,0.0027</t>
+  </si>
+  <si>
+    <t>0.0026,0.1358,0.9640,0.0062</t>
+  </si>
+  <si>
+    <t>0.0143,0.0081,0.9748,0.0013</t>
+  </si>
+  <si>
+    <t>0.0034,0.0025,0.9934,0.0006</t>
+  </si>
+  <si>
+    <t>0.2586,0.0053,0.8323,0.0035</t>
+  </si>
+  <si>
+    <t>0.0060,0.0072,0.9895,0.0013</t>
+  </si>
+  <si>
+    <t>0.0342,0.0313,0.9543,0.0012</t>
+  </si>
+  <si>
+    <t>0.0277,0.1027,0.9364,0.0086</t>
+  </si>
+  <si>
+    <t>0.5819,0.1731,0.2123,0.0205</t>
+  </si>
+  <si>
+    <t>0.8111,0.0175,0.1962,0.0054</t>
+  </si>
+  <si>
+    <t>0.9641,0.0041,0.0190,0.0008</t>
+  </si>
+  <si>
+    <t>0.9815,0.0149,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9870,0.0093,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9828,0.0115,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.9797,0.0122,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9921,0.0013,0.0003,0.0021</t>
+  </si>
+  <si>
+    <t>0.9863,0.0059,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.9914,0.0036,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9597,0.0034,0.0002,0.0169</t>
+  </si>
+  <si>
+    <t>0.0146,0.0700,0.9393,0.0022</t>
+  </si>
+  <si>
+    <t>0.0036,0.0049,0.9916,0.0010</t>
+  </si>
+  <si>
+    <t>0.0091,0.0193,0.9812,0.0011</t>
+  </si>
+  <si>
+    <t>0.1259,0.0143,0.8980,0.0029</t>
+  </si>
+  <si>
+    <t>0.0041,0.0031,0.9823,0.0144</t>
+  </si>
+  <si>
+    <t>0.0979,0.0161,0.7965,0.1343</t>
+  </si>
+  <si>
+    <t>0.0148,0.0204,0.9606,0.0174</t>
+  </si>
+  <si>
+    <t>0.0097,0.0082,0.9635,0.0463</t>
+  </si>
+  <si>
+    <t>0.5280,0.0022,0.0707,0.3599</t>
+  </si>
+  <si>
+    <t>0.0246,0.0098,0.0004,0.9887</t>
+  </si>
+  <si>
+    <t>0.0291,0.0035,0.0004,0.9914</t>
+  </si>
+  <si>
+    <t>0.0029,0.0001,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.4921,0.0644,0.0043,0.4315</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2581,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4639,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5336,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
